--- a/hydration/samples/3_invoices.xlsx
+++ b/hydration/samples/3_invoices.xlsx
@@ -499,10 +499,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>INV_001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>out_invoice</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>emp_alice</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Software License</t>
